--- a/Stundenliste_neu(1).xlsx
+++ b/Stundenliste_neu(1).xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VR1\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arthur\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B86D934-C54C-4E8A-AD92-26FE1323184E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D5FCE1-1C80-4A04-970C-92736A2DCF52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="20625" xr2:uid="{904973F5-B02B-4666-A03D-BB66738E721E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{904973F5-B02B-4666-A03D-BB66738E721E}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="86">
   <si>
     <t>Tag</t>
   </si>
@@ -291,6 +291,9 @@
   </si>
   <si>
     <t>Server, Besprechung</t>
+  </si>
+  <si>
+    <t>Auto Szene repariert + erweitert</t>
   </si>
 </sst>
 </file>
@@ -426,8 +429,8 @@
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Prozent" xfId="1" builtinId="5"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -644,7 +647,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="de-DE"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -906,7 +909,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.6341374269005815</c:v>
+                  <c:v>0.65058479532163416</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1973,9 +1976,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 – 2022">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2013,7 +2016,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 – 2022">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2119,7 +2122,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 – 2022">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2271,7 +2274,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{730198CE-52B5-4F02-9B4B-1774B163D30B}">
   <sheetPr codeName="Tabelle1"/>
   <dimension ref="A1:Q77"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.42578125" customWidth="1"/>
@@ -2446,23 +2449,23 @@
       </c>
       <c r="M4" s="11">
         <f>SUM(J5,J8,J9,J11)</f>
-        <v>4.8194444444444446</v>
+        <v>4.9444444444444446</v>
       </c>
       <c r="N4" s="18">
         <f t="shared" ref="N4:N5" si="2">M4</f>
-        <v>4.8194444444444446</v>
+        <v>4.9444444444444446</v>
       </c>
       <c r="O4" s="18">
         <f t="shared" ref="O4:O5" si="3">N4/60</f>
-        <v>8.0324074074074076E-2</v>
+        <v>8.2407407407407415E-2</v>
       </c>
       <c r="P4" s="22">
         <f t="shared" si="1"/>
-        <v>4.4624485596707821E-2</v>
+        <v>4.5781893004115233E-2</v>
       </c>
       <c r="Q4" s="21">
         <f t="shared" ref="Q4:Q5" si="4">(P4*1421.05263157894)/100</f>
-        <v>0.6341374269005815</v>
+        <v>0.65058479532163416</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -2494,7 +2497,7 @@
       </c>
       <c r="J5" s="10">
         <f>SUMIF(Stundenliste[Wer],I5,Stundenliste[Stunden])</f>
-        <v>1.1736111111111112</v>
+        <v>1.2986111111111112</v>
       </c>
       <c r="L5" t="s">
         <v>9</v>
@@ -2596,7 +2599,7 @@
       </c>
       <c r="M7" s="15">
         <f>SUM(F2:F77)</f>
-        <v>8.9861111111111143</v>
+        <v>9.1111111111111143</v>
       </c>
       <c r="N7">
         <v>180</v>
@@ -2635,7 +2638,7 @@
       </c>
       <c r="M8" s="16">
         <f>TEXT(M7,"[h]")+TEXT(M7,"mm")/60</f>
-        <v>215.66666666666666</v>
+        <v>218.66666666666666</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -4313,17 +4316,27 @@
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="str">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="B75" s="3"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="5" t="str">
+        <v>Do.</v>
+      </c>
+      <c r="B75" s="3">
+        <v>46086</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D75" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E75" s="4">
+        <v>0.875</v>
+      </c>
+      <c r="F75" s="5">
         <f>IF(E75&gt;D75,E75-D75,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D75-E75),""))</f>
-        <v/>
-      </c>
-      <c r="G75" s="2"/>
+        <v>0.125</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="str">
@@ -4368,20 +4381,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <ReferenceId xmlns="d9f85066-e658-4e34-914c-f198c2427564" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <ReferenceId xmlns="d9f85066-e658-4e34-914c-f198c2427564" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4529,14 +4542,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A879EED-63D4-4BD6-ABDC-8DEB19CAAEDF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57E083A2-B59E-4178-BBDB-6F72551558F7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -4550,6 +4555,14 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="becce21f-4543-4ee3-84d8-746b4cf7c34b"/>
     <ds:schemaRef ds:uri="d9f85066-e658-4e34-914c-f198c2427564"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A879EED-63D4-4BD6-ABDC-8DEB19CAAEDF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Stundenliste_neu(1).xlsx
+++ b/Stundenliste_neu(1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arthur\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arthur.peer\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D5FCE1-1C80-4A04-970C-92736A2DCF52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B460BA97-566C-4DDD-B070-70B78D07C376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{904973F5-B02B-4666-A03D-BB66738E721E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{904973F5-B02B-4666-A03D-BB66738E721E}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="91">
   <si>
     <t>Tag</t>
   </si>
@@ -191,9 +191,6 @@
     <t>Vr-Brillen und Meta reaperieren + Standalone</t>
   </si>
   <si>
-    <t>Fehlerbehben (Debugging)</t>
-  </si>
-  <si>
     <t>Programmiert</t>
   </si>
   <si>
@@ -294,6 +291,24 @@
   </si>
   <si>
     <t>Auto Szene repariert + erweitert</t>
+  </si>
+  <si>
+    <t>Müllberg-Szene begonnen</t>
+  </si>
+  <si>
+    <t>Auto Szene repariert</t>
+  </si>
+  <si>
+    <t>Müllberg-Szene, Auto-Szene</t>
+  </si>
+  <si>
+    <t>Fehlerbeheben (Debugging)</t>
+  </si>
+  <si>
+    <t>Stundenliste aktualisieren</t>
+  </si>
+  <si>
+    <t>Zeitmanagement</t>
   </si>
 </sst>
 </file>
@@ -393,7 +408,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -427,10 +442,11 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Prozent" xfId="1" builtinId="5"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -647,7 +663,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="de-DE"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -809,7 +825,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.82785087719297801</c:v>
+                  <c:v>0.83333333333332915</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -909,7 +925,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.65058479532163416</c:v>
+                  <c:v>0.70175438596490847</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1917,10 +1933,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD71F5EC-BCBD-4D95-9F21-060EF7779827}" name="Stundenliste" displayName="Stundenliste" ref="A1:G77" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A1:G77" xr:uid="{730AE997-56E9-481C-8C9C-45C7D9E3EFFC}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G41">
-    <sortCondition ref="B1:B41"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD71F5EC-BCBD-4D95-9F21-060EF7779827}" name="Stundenliste" displayName="Stundenliste" ref="A1:G80" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A1:G80" xr:uid="{730AE997-56E9-481C-8C9C-45C7D9E3EFFC}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G80">
+    <sortCondition ref="B1:B80"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{AD59871A-76CC-45F6-8F91-44F7ED02573E}" name="Tag" dataDxfId="14">
@@ -1976,9 +1992,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2016,7 +2032,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2122,7 +2138,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2273,8 +2289,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{730198CE-52B5-4F02-9B4B-1774B163D30B}">
   <sheetPr codeName="Tabelle1"/>
-  <dimension ref="A1:Q77"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q80"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.42578125" customWidth="1"/>
@@ -2310,7 +2326,7 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="str">
-        <f t="shared" ref="A2:A34" si="0">IF(ISNUMBER(B2),LEFT(TEXT(B2,"TTTT"),2)&amp;".","")</f>
+        <f>IF(ISNUMBER(B2),LEFT(TEXT(B2,"TTTT"),2)&amp;".","")</f>
         <v>So.</v>
       </c>
       <c r="B2" s="3">
@@ -2359,7 +2375,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B3),LEFT(TEXT(B3,"TTTT"),2)&amp;".","")</f>
         <v>Di.</v>
       </c>
       <c r="B3" s="3">
@@ -2394,28 +2410,28 @@
       </c>
       <c r="M3" s="11">
         <f>SUM(J4,J7,J8,J11)</f>
-        <v>6.291666666666667</v>
+        <v>6.3333333333333339</v>
       </c>
       <c r="N3" s="18">
         <f>M3</f>
-        <v>6.291666666666667</v>
+        <v>6.3333333333333339</v>
       </c>
       <c r="O3" s="18">
         <f>N3/60</f>
-        <v>0.10486111111111111</v>
+        <v>0.10555555555555557</v>
       </c>
       <c r="P3" s="22">
-        <f t="shared" ref="P3:P6" si="1">(O3/180)*100</f>
-        <v>5.8256172839506168E-2</v>
+        <f t="shared" ref="P3:P6" si="0">(O3/180)*100</f>
+        <v>5.8641975308641986E-2</v>
       </c>
       <c r="Q3" s="21">
         <f>(P3*1421.05263157894)/100</f>
-        <v>0.82785087719297801</v>
+        <v>0.83333333333332915</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B4),LEFT(TEXT(B4,"TTTT"),2)&amp;".","")</f>
         <v>Di.</v>
       </c>
       <c r="B4" s="3">
@@ -2449,28 +2465,28 @@
       </c>
       <c r="M4" s="11">
         <f>SUM(J5,J8,J9,J11)</f>
-        <v>4.9444444444444446</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="N4" s="18">
-        <f t="shared" ref="N4:N5" si="2">M4</f>
-        <v>4.9444444444444446</v>
+        <f t="shared" ref="N4:N5" si="1">M4</f>
+        <v>5.333333333333333</v>
       </c>
       <c r="O4" s="18">
-        <f t="shared" ref="O4:O5" si="3">N4/60</f>
-        <v>8.2407407407407415E-2</v>
+        <f t="shared" ref="O4:O5" si="2">N4/60</f>
+        <v>8.8888888888888878E-2</v>
       </c>
       <c r="P4" s="22">
-        <f t="shared" si="1"/>
-        <v>4.5781893004115233E-2</v>
+        <f t="shared" si="0"/>
+        <v>4.9382716049382706E-2</v>
       </c>
       <c r="Q4" s="21">
-        <f t="shared" ref="Q4:Q5" si="4">(P4*1421.05263157894)/100</f>
-        <v>0.65058479532163416</v>
+        <f t="shared" ref="Q4:Q5" si="3">(P4*1421.05263157894)/100</f>
+        <v>0.70175438596490847</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B5),LEFT(TEXT(B5,"TTTT"),2)&amp;".","")</f>
         <v>Di.</v>
       </c>
       <c r="B5" s="3">
@@ -2497,7 +2513,7 @@
       </c>
       <c r="J5" s="10">
         <f>SUMIF(Stundenliste[Wer],I5,Stundenliste[Stunden])</f>
-        <v>1.2986111111111112</v>
+        <v>1.6458333333333335</v>
       </c>
       <c r="L5" t="s">
         <v>9</v>
@@ -2507,25 +2523,25 @@
         <v>5.1874999999999991</v>
       </c>
       <c r="N5" s="18">
+        <f t="shared" si="1"/>
+        <v>5.1874999999999991</v>
+      </c>
+      <c r="O5" s="18">
         <f t="shared" si="2"/>
-        <v>5.1874999999999991</v>
-      </c>
-      <c r="O5" s="18">
+        <v>8.6458333333333318E-2</v>
+      </c>
+      <c r="P5" s="22">
+        <f t="shared" si="0"/>
+        <v>4.8032407407407399E-2</v>
+      </c>
+      <c r="Q5" s="21">
         <f t="shared" si="3"/>
-        <v>8.6458333333333318E-2</v>
-      </c>
-      <c r="P5" s="22">
-        <f t="shared" si="1"/>
-        <v>4.8032407407407399E-2</v>
-      </c>
-      <c r="Q5" s="21">
-        <f t="shared" si="4"/>
         <v>0.68256578947368052</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B6),LEFT(TEXT(B6,"TTTT"),2)&amp;".","")</f>
         <v>Di.</v>
       </c>
       <c r="B6" s="3">
@@ -2558,7 +2574,7 @@
         <v>180</v>
       </c>
       <c r="P6" s="20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="Q6" s="21">
@@ -2568,7 +2584,7 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B7),LEFT(TEXT(B7,"TTTT"),2)&amp;".","")</f>
         <v>Di.</v>
       </c>
       <c r="B7" s="3">
@@ -2598,8 +2614,8 @@
         <v>0.77083333333333326</v>
       </c>
       <c r="M7" s="15">
-        <f>SUM(F2:F77)</f>
-        <v>9.1111111111111143</v>
+        <f>SUM(F2:F80)</f>
+        <v>9.5000000000000053</v>
       </c>
       <c r="N7">
         <v>180</v>
@@ -2607,7 +2623,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B8),LEFT(TEXT(B8,"TTTT"),2)&amp;".","")</f>
         <v>Sa.</v>
       </c>
       <c r="B8" s="3">
@@ -2634,16 +2650,16 @@
       </c>
       <c r="J8" s="10">
         <f>SUMIF(Stundenliste[Wer],I8,Stundenliste[Stunden])</f>
-        <v>0.75</v>
+        <v>0.79166666666666674</v>
       </c>
       <c r="M8" s="16">
         <f>TEXT(M7,"[h]")+TEXT(M7,"mm")/60</f>
-        <v>218.66666666666666</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B9),LEFT(TEXT(B9,"TTTT"),2)&amp;".","")</f>
         <v>Fr.</v>
       </c>
       <c r="B9" s="3">
@@ -2675,7 +2691,7 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B10),LEFT(TEXT(B10,"TTTT"),2)&amp;".","")</f>
         <v>Sa.</v>
       </c>
       <c r="B10" s="3">
@@ -2702,7 +2718,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B11),LEFT(TEXT(B11,"TTTT"),2)&amp;".","")</f>
         <v>Mi.</v>
       </c>
       <c r="B11" s="3">
@@ -2734,7 +2750,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B12),LEFT(TEXT(B12,"TTTT"),2)&amp;".","")</f>
         <v>So.</v>
       </c>
       <c r="B12" s="3">
@@ -2759,7 +2775,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B13),LEFT(TEXT(B13,"TTTT"),2)&amp;".","")</f>
         <v>Fr.</v>
       </c>
       <c r="B13" s="3">
@@ -2787,27 +2803,27 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Fr.</v>
+        <f>IF(ISNUMBER(B14),LEFT(TEXT(B14,"TTTT"),2)&amp;".","")</f>
+        <v>Mo.</v>
       </c>
       <c r="B14" s="3">
-        <v>45968</v>
+        <v>45957</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="D14" s="4">
-        <v>0.625</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="E14" s="4">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="F14" s="12">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F14" s="5">
         <f>IF(E14&gt;D14,E14-D14,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D14-E14),""))</f>
-        <v>8.333333333333337E-2</v>
+        <v>0.12499999999999994</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I14" s="14"/>
       <c r="J14" s="9"/>
@@ -2815,120 +2831,120 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Sa.</v>
+        <f>IF(ISNUMBER(B15),LEFT(TEXT(B15,"TTTT"),2)&amp;".","")</f>
+        <v>Mi.</v>
       </c>
       <c r="B15" s="3">
-        <v>45969</v>
+        <v>45959</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="D15" s="4">
-        <v>0.58333333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E15" s="4">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="F15" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F15" s="5">
         <f>IF(E15&gt;D15,E15-D15,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D15-E15),""))</f>
-        <v>0.33333333333333326</v>
+        <v>0.16666666666666674</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Sa.</v>
+        <f>IF(ISNUMBER(B16),LEFT(TEXT(B16,"TTTT"),2)&amp;".","")</f>
+        <v>Do.</v>
       </c>
       <c r="B16" s="3">
-        <v>45969</v>
+        <v>45960</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="D16" s="4">
-        <v>0.58333333333333337</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E16" s="4">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="F16" s="12">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="F16" s="5">
         <f>IF(E16&gt;D16,E16-D16,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D16-E16),""))</f>
-        <v>0.25</v>
+        <v>8.3333333333333259E-2</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Mi.</v>
+        <f>IF(ISNUMBER(B17),LEFT(TEXT(B17,"TTTT"),2)&amp;".","")</f>
+        <v>Sa.</v>
       </c>
       <c r="B17" s="3">
-        <v>45973</v>
+        <v>45962</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="D17" s="4">
-        <v>0.49305555555555558</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="E17" s="4">
-        <v>0.52777777777777779</v>
-      </c>
-      <c r="F17" s="12">
+        <v>0.875</v>
+      </c>
+      <c r="F17" s="5">
         <f>IF(E17&gt;D17,E17-D17,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D17-E17),""))</f>
-        <v>3.472222222222221E-2</v>
+        <v>8.333333333333337E-2</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Mi.</v>
+        <f>IF(ISNUMBER(B18),LEFT(TEXT(B18,"TTTT"),2)&amp;".","")</f>
+        <v>So.</v>
       </c>
       <c r="B18" s="3">
-        <v>45980</v>
+        <v>45963</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="D18" s="4">
-        <v>0.70833333333333304</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E18" s="4">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F18" s="12">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="F18" s="5">
         <f>IF(E18&gt;D18,E18-D18,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D18-E18),""))</f>
-        <v>8.3333333333333592E-2</v>
+        <v>8.3333333333333259E-2</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Do.</v>
+        <f>IF(ISNUMBER(B19),LEFT(TEXT(B19,"TTTT"),2)&amp;".","")</f>
+        <v>Fr.</v>
       </c>
       <c r="B19" s="3">
-        <v>45981</v>
+        <v>45968</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D19" s="4">
-        <v>0.66666666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="E19" s="4">
-        <v>0.75</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F19" s="12">
         <f>IF(E19&gt;D19,E19-D19,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D19-E19),""))</f>
@@ -2940,74 +2956,74 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Fr.</v>
+        <f>IF(ISNUMBER(B20),LEFT(TEXT(B20,"TTTT"),2)&amp;".","")</f>
+        <v>Sa.</v>
       </c>
       <c r="B20" s="3">
-        <v>45982</v>
+        <v>45969</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" s="4">
-        <v>0.5</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="E20" s="4">
-        <v>0.625</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="F20" s="12">
         <f>IF(E20&gt;D20,E20-D20,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D20-E20),""))</f>
-        <v>0.125</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Fr.</v>
+        <f>IF(ISNUMBER(B21),LEFT(TEXT(B21,"TTTT"),2)&amp;".","")</f>
+        <v>Sa.</v>
       </c>
       <c r="B21" s="3">
-        <v>45982</v>
+        <v>45969</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D21" s="4">
         <v>0.58333333333333337</v>
       </c>
       <c r="E21" s="4">
-        <v>0.66666666666666663</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F21" s="12">
         <f>IF(E21&gt;D21,E21-D21,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D21-E21),""))</f>
-        <v>8.3333333333333259E-2</v>
+        <v>0.25</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Sa.</v>
+        <f>IF(ISNUMBER(B22),LEFT(TEXT(B22,"TTTT"),2)&amp;".","")</f>
+        <v>Mi.</v>
       </c>
       <c r="B22" s="3">
-        <v>45983</v>
+        <v>45973</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D22" s="4">
-        <v>0.33333333333333331</v>
+        <v>0.49305555555555558</v>
       </c>
       <c r="E22" s="4">
-        <v>0.45833333333333331</v>
+        <v>0.52777777777777779</v>
       </c>
       <c r="F22" s="12">
         <f>IF(E22&gt;D22,E22-D22,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D22-E22),""))</f>
-        <v>0.125</v>
+        <v>3.472222222222221E-2</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>7</v>
@@ -3015,149 +3031,149 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Sa.</v>
+        <f>IF(ISNUMBER(B23),LEFT(TEXT(B23,"TTTT"),2)&amp;".","")</f>
+        <v>Do.</v>
       </c>
       <c r="B23" s="3">
-        <v>45990</v>
+        <v>45974</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="D23" s="4">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="E23" s="17">
-        <v>1</v>
-      </c>
-      <c r="F23" s="12">
+        <v>0.625</v>
+      </c>
+      <c r="E23" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F23" s="5">
         <f>IF(E23&gt;D23,E23-D23,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D23-E23),""))</f>
-        <v>0.16666666666666663</v>
+        <v>0.125</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Fr.</v>
+        <f>IF(ISNUMBER(B24),LEFT(TEXT(B24,"TTTT"),2)&amp;".","")</f>
+        <v>Mi.</v>
       </c>
       <c r="B24" s="3">
-        <v>45996</v>
+        <v>45980</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D24" s="4">
-        <v>0.70833333333333337</v>
+        <v>0.70833333333333304</v>
       </c>
       <c r="E24" s="4">
         <v>0.79166666666666663</v>
       </c>
       <c r="F24" s="12">
         <f>IF(E24&gt;D24,E24-D24,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D24-E24),""))</f>
-        <v>8.3333333333333259E-2</v>
+        <v>8.3333333333333592E-2</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Mo.</v>
+        <f>IF(ISNUMBER(B25),LEFT(TEXT(B25,"TTTT"),2)&amp;".","")</f>
+        <v>Mi.</v>
       </c>
       <c r="B25" s="3">
-        <v>45999</v>
+        <v>45980</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="D25" s="4">
-        <v>0.45833333333333331</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="E25" s="4">
-        <v>0.49305555555555558</v>
-      </c>
-      <c r="F25" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F25" s="5">
         <f>IF(E25&gt;D25,E25-D25,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D25-E25),""))</f>
-        <v>3.4722222222222265E-2</v>
+        <v>8.3333333333333259E-2</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Mi.</v>
+        <f>IF(ISNUMBER(B26),LEFT(TEXT(B26,"TTTT"),2)&amp;".","")</f>
+        <v>Do.</v>
       </c>
       <c r="B26" s="3">
-        <v>46001</v>
+        <v>45981</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D26" s="4">
-        <v>0.52777777777777779</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E26" s="4">
-        <v>0.67361111111111116</v>
+        <v>0.75</v>
       </c>
       <c r="F26" s="12">
         <f>IF(E26&gt;D26,E26-D26,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D26-E26),""))</f>
-        <v>0.14583333333333337</v>
+        <v>8.333333333333337E-2</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Mi.</v>
+        <f>IF(ISNUMBER(B27),LEFT(TEXT(B27,"TTTT"),2)&amp;".","")</f>
+        <v>Fr.</v>
       </c>
       <c r="B27" s="3">
-        <v>46001</v>
+        <v>45982</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D27" s="9">
-        <v>0.58333333333333304</v>
+        <v>28</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0.5</v>
       </c>
       <c r="E27" s="4">
-        <v>0.67361111111111116</v>
+        <v>0.625</v>
       </c>
       <c r="F27" s="12">
         <f>IF(E27&gt;D27,E27-D27,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D27-E27),""))</f>
-        <v>9.0277777777778123E-2</v>
+        <v>0.125</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Mi.</v>
+        <f>IF(ISNUMBER(B28),LEFT(TEXT(B28,"TTTT"),2)&amp;".","")</f>
+        <v>Fr.</v>
       </c>
       <c r="B28" s="3">
-        <v>46001</v>
+        <v>45982</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D28" s="4">
-        <v>0.49305555555555558</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="E28" s="4">
-        <v>0.52777777777777779</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F28" s="12">
         <f>IF(E28&gt;D28,E28-D28,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D28-E28),""))</f>
-        <v>3.472222222222221E-2</v>
+        <v>8.3333333333333259E-2</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>7</v>
@@ -3165,24 +3181,24 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Mo.</v>
+        <f>IF(ISNUMBER(B29),LEFT(TEXT(B29,"TTTT"),2)&amp;".","")</f>
+        <v>Sa.</v>
       </c>
       <c r="B29" s="3">
-        <v>46013</v>
+        <v>45983</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D29" s="4">
-        <v>0.58333333333333337</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E29" s="4">
-        <v>0.67361111111111116</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="F29" s="12">
         <f>IF(E29&gt;D29,E29-D29,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D29-E29),""))</f>
-        <v>9.027777777777779E-2</v>
+        <v>0.125</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>7</v>
@@ -3190,49 +3206,49 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Mo.</v>
+        <f>IF(ISNUMBER(B30),LEFT(TEXT(B30,"TTTT"),2)&amp;".","")</f>
+        <v>Sa.</v>
       </c>
       <c r="B30" s="3">
-        <v>46013</v>
+        <v>45990</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D30" s="4">
-        <v>0.49305555555555558</v>
-      </c>
-      <c r="E30" s="4">
-        <v>0.52777777777777779</v>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="E30" s="17">
+        <v>1</v>
       </c>
       <c r="F30" s="12">
         <f>IF(E30&gt;D30,E30-D30,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D30-E30),""))</f>
-        <v>3.472222222222221E-2</v>
+        <v>0.16666666666666663</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B31),LEFT(TEXT(B31,"TTTT"),2)&amp;".","")</f>
         <v>Fr.</v>
       </c>
       <c r="B31" s="3">
-        <v>46017</v>
+        <v>45996</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D31" s="4">
-        <v>0.75</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="E31" s="4">
-        <v>1</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="F31" s="12">
         <f>IF(E31&gt;D31,E31-D31,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D31-E31),""))</f>
-        <v>0.25</v>
+        <v>8.3333333333333259E-2</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>10</v>
@@ -3240,149 +3256,149 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Fr.</v>
+        <f>IF(ISNUMBER(B32),LEFT(TEXT(B32,"TTTT"),2)&amp;".","")</f>
+        <v>Mo.</v>
       </c>
       <c r="B32" s="3">
-        <v>46017</v>
+        <v>45999</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D32" s="4">
-        <v>0.77083333333333337</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="E32" s="4">
-        <v>0.9375</v>
+        <v>0.49305555555555558</v>
       </c>
       <c r="F32" s="12">
         <f>IF(E32&gt;D32,E32-D32,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D32-E32),""))</f>
-        <v>0.16666666666666663</v>
+        <v>3.4722222222222265E-2</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Mo.</v>
+        <f>IF(ISNUMBER(B33),LEFT(TEXT(B33,"TTTT"),2)&amp;".","")</f>
+        <v>Mi.</v>
       </c>
       <c r="B33" s="3">
-        <v>46020</v>
+        <v>46001</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D33" s="4">
-        <v>0.5</v>
+        <v>0.52777777777777779</v>
       </c>
       <c r="E33" s="4">
-        <v>0.60416666666666663</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="F33" s="12">
         <f>IF(E33&gt;D33,E33-D33,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D33-E33),""))</f>
-        <v>0.10416666666666663</v>
+        <v>0.14583333333333337</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Mo.</v>
+        <f>IF(ISNUMBER(B34),LEFT(TEXT(B34,"TTTT"),2)&amp;".","")</f>
+        <v>Mi.</v>
       </c>
       <c r="B34" s="3">
-        <v>46020</v>
+        <v>46001</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D34" s="4">
-        <v>0.5</v>
+        <v>25</v>
+      </c>
+      <c r="D34" s="9">
+        <v>0.58333333333333304</v>
       </c>
       <c r="E34" s="4">
-        <v>0.75</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="F34" s="12">
         <f>IF(E34&gt;D34,E34-D34,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D34-E34),""))</f>
-        <v>0.25</v>
+        <v>9.0277777777778123E-2</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="str">
-        <f t="shared" ref="A35:A41" si="5">IF(ISNUMBER(B35),LEFT(TEXT(B35,"TTTT"),2)&amp;".","")</f>
-        <v>Fr.</v>
+        <f>IF(ISNUMBER(B35),LEFT(TEXT(B35,"TTTT"),2)&amp;".","")</f>
+        <v>Mi.</v>
       </c>
       <c r="B35" s="3">
-        <v>46024</v>
+        <v>46001</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D35" s="4">
-        <v>0.5</v>
+        <v>0.49305555555555558</v>
       </c>
       <c r="E35" s="4">
-        <v>0.58333333333333337</v>
+        <v>0.52777777777777779</v>
       </c>
       <c r="F35" s="12">
         <f>IF(E35&gt;D35,E35-D35,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D35-E35),""))</f>
-        <v>8.333333333333337E-2</v>
+        <v>3.472222222222221E-2</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>Sa.</v>
+        <f>IF(ISNUMBER(B36),LEFT(TEXT(B36,"TTTT"),2)&amp;".","")</f>
+        <v>Mo.</v>
       </c>
       <c r="B36" s="3">
-        <v>46025</v>
+        <v>46013</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D36" s="4">
-        <v>0.5</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="E36" s="4">
-        <v>0.58333333333333337</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="F36" s="12">
         <f>IF(E36&gt;D36,E36-D36,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D36-E36),""))</f>
-        <v>8.333333333333337E-2</v>
+        <v>9.027777777777779E-2</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>So.</v>
+        <f>IF(ISNUMBER(B37),LEFT(TEXT(B37,"TTTT"),2)&amp;".","")</f>
+        <v>Mo.</v>
       </c>
       <c r="B37" s="3">
-        <v>46026</v>
+        <v>46013</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="D37" s="4">
-        <v>0.70833333333333337</v>
+        <v>0.49305555555555558</v>
       </c>
       <c r="E37" s="4">
-        <v>0.875</v>
+        <v>0.52777777777777779</v>
       </c>
       <c r="F37" s="12">
         <f>IF(E37&gt;D37,E37-D37,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D37-E37),""))</f>
-        <v>0.16666666666666663</v>
+        <v>3.472222222222221E-2</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>7</v>
@@ -3390,120 +3406,120 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISNUMBER(B38),LEFT(TEXT(B38,"TTTT"),2)&amp;".","")</f>
         <v>Fr.</v>
       </c>
       <c r="B38" s="3">
-        <v>46031</v>
+        <v>46017</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="D38" s="4">
-        <v>0.30902777777777779</v>
+        <v>0.75</v>
       </c>
       <c r="E38" s="4">
-        <v>0.35069444444444442</v>
+        <v>1</v>
       </c>
       <c r="F38" s="12">
         <f>IF(E38&gt;D38,E38-D38,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D38-E38),""))</f>
-        <v>4.166666666666663E-2</v>
+        <v>0.25</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="str">
         <f>IF(ISNUMBER(B39),LEFT(TEXT(B39,"TTTT"),2)&amp;".","")</f>
-        <v>Mi.</v>
+        <v>Fr.</v>
       </c>
       <c r="B39" s="3">
-        <v>46050</v>
+        <v>46017</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="D39" s="4">
-        <v>0.72222222222222221</v>
+        <v>0.77083333333333337</v>
       </c>
       <c r="E39" s="4">
-        <v>0.76388888888888884</v>
+        <v>0.9375</v>
       </c>
       <c r="F39" s="12">
         <f>IF(E39&gt;D39,E39-D39,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D39-E39),""))</f>
-        <v>4.166666666666663E-2</v>
+        <v>0.16666666666666663</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>Fr.</v>
+        <f>IF(ISNUMBER(B40),LEFT(TEXT(B40,"TTTT"),2)&amp;".","")</f>
+        <v>Mo.</v>
       </c>
       <c r="B40" s="3">
-        <v>46038</v>
+        <v>46020</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="D40" s="4">
-        <v>0.66666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="E40" s="4">
-        <v>0.83333333333333337</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="F40" s="12">
         <f>IF(E40&gt;D40,E40-D40,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D40-E40),""))</f>
-        <v>0.16666666666666674</v>
+        <v>0.10416666666666663</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>Sa.</v>
+        <f>IF(ISNUMBER(B41),LEFT(TEXT(B41,"TTTT"),2)&amp;".","")</f>
+        <v>Mo.</v>
       </c>
       <c r="B41" s="3">
-        <v>46039</v>
+        <v>46020</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="D41" s="4">
-        <v>0.66666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="E41" s="4">
-        <v>0.83333333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="F41" s="12">
         <f>IF(E41&gt;D41,E41-D41,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D41-E41),""))</f>
-        <v>0.16666666666666674</v>
+        <v>0.25</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="str">
         <f>IF(ISNUMBER(B42),LEFT(TEXT(B42,"TTTT"),2)&amp;".","")</f>
-        <v>Di.</v>
+        <v>Fr.</v>
       </c>
       <c r="B42" s="3">
-        <v>46042</v>
+        <v>46024</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D42" s="4">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="E42" s="17">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="E42" s="4">
+        <v>0.58333333333333337</v>
       </c>
       <c r="F42" s="12">
         <f>IF(E42&gt;D42,E42-D42,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D42-E42),""))</f>
@@ -3516,19 +3532,19 @@
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="str">
         <f>IF(ISNUMBER(B43),LEFT(TEXT(B43,"TTTT"),2)&amp;".","")</f>
-        <v>Mi.</v>
+        <v>Sa.</v>
       </c>
       <c r="B43" s="3">
-        <v>46057</v>
+        <v>46025</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D43" s="4">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="E43" s="17">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="E43" s="4">
+        <v>0.58333333333333337</v>
       </c>
       <c r="F43" s="12">
         <f>IF(E43&gt;D43,E43-D43,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D43-E43),""))</f>
@@ -3541,488 +3557,488 @@
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="str">
         <f>IF(ISNUMBER(B44),LEFT(TEXT(B44,"TTTT"),2)&amp;".","")</f>
-        <v>Sa.</v>
+        <v>So.</v>
       </c>
       <c r="B44" s="3">
-        <v>46067</v>
+        <v>46026</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D44" s="4">
-        <v>0.66666666666666663</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="E44" s="4">
         <v>0.875</v>
       </c>
       <c r="F44" s="12">
         <f>IF(E44&gt;D44,E44-D44,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D44-E44),""))</f>
-        <v>0.20833333333333337</v>
+        <v>0.16666666666666663</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="str">
         <f>IF(ISNUMBER(B45),LEFT(TEXT(B45,"TTTT"),2)&amp;".","")</f>
-        <v>Sa.</v>
+        <v>Fr.</v>
       </c>
       <c r="B45" s="3">
-        <v>46067</v>
+        <v>46031</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D45" s="4">
-        <v>0.58333333333333337</v>
+        <v>0.30902777777777779</v>
       </c>
       <c r="E45" s="4">
-        <v>0.75</v>
+        <v>0.35069444444444442</v>
       </c>
       <c r="F45" s="12">
         <f>IF(E45&gt;D45,E45-D45,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D45-E45),""))</f>
-        <v>0.16666666666666663</v>
+        <v>4.166666666666663E-2</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="str">
         <f>IF(ISNUMBER(B46),LEFT(TEXT(B46,"TTTT"),2)&amp;".","")</f>
-        <v>Mo.</v>
+        <v>Fr.</v>
       </c>
       <c r="B46" s="3">
-        <v>46062</v>
+        <v>46038</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D46" s="4">
-        <v>0.70833333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E46" s="4">
-        <v>0.75</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F46" s="12">
         <f>IF(E46&gt;D46,E46-D46,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D46-E46),""))</f>
-        <v>4.166666666666663E-2</v>
+        <v>0.16666666666666674</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="str">
-        <f t="shared" ref="A47:A49" si="6">IF(ISNUMBER(B47),LEFT(TEXT(B47,"TTTT"),2)&amp;".","")</f>
+        <f>IF(ISNUMBER(B47),LEFT(TEXT(B47,"TTTT"),2)&amp;".","")</f>
         <v>Sa.</v>
       </c>
       <c r="B47" s="3">
-        <v>46067</v>
+        <v>46039</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D47" s="4">
-        <v>0.58333333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E47" s="4">
-        <v>0.75</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F47" s="12">
         <f>IF(E47&gt;D47,E47-D47,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D47-E47),""))</f>
-        <v>0.16666666666666663</v>
+        <v>0.16666666666666674</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Fr.</v>
+        <f>IF(ISNUMBER(B48),LEFT(TEXT(B48,"TTTT"),2)&amp;".","")</f>
+        <v>Di.</v>
       </c>
       <c r="B48" s="3">
-        <v>46073</v>
+        <v>46042</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D48" s="4">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="E48" s="4">
-        <v>0.66666666666666663</v>
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="E48" s="17">
+        <v>1</v>
       </c>
       <c r="F48" s="12">
         <f>IF(E48&gt;D48,E48-D48,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D48-E48),""))</f>
-        <v>0.125</v>
+        <v>8.333333333333337E-2</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Sa.</v>
+        <f>IF(ISNUMBER(B49),LEFT(TEXT(B49,"TTTT"),2)&amp;".","")</f>
+        <v>Mi.</v>
       </c>
       <c r="B49" s="3">
-        <v>46074</v>
+        <v>46050</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="D49" s="4">
-        <v>0.75</v>
+        <v>0.72222222222222221</v>
       </c>
       <c r="E49" s="4">
-        <v>0</v>
+        <v>0.76388888888888884</v>
       </c>
       <c r="F49" s="12">
         <f>IF(E49&gt;D49,E49-D49,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D49-E49),""))</f>
-        <v>0.25</v>
+        <v>4.166666666666663E-2</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="str">
         <f>IF(ISNUMBER(B50),LEFT(TEXT(B50,"TTTT"),2)&amp;".","")</f>
-        <v>Di.</v>
+        <v>Mi.</v>
       </c>
       <c r="B50" s="3">
-        <v>46077</v>
+        <v>46057</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D50" s="4">
-        <v>0.75</v>
-      </c>
-      <c r="E50" s="4">
-        <v>0.8125</v>
-      </c>
-      <c r="F50" s="5">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="E50" s="17">
+        <v>1</v>
+      </c>
+      <c r="F50" s="12">
         <f>IF(E50&gt;D50,E50-D50,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D50-E50),""))</f>
-        <v>6.25E-2</v>
+        <v>8.333333333333337E-2</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="str">
         <f>IF(ISNUMBER(B51),LEFT(TEXT(B51,"TTTT"),2)&amp;".","")</f>
-        <v>Fr.</v>
+        <v>Mo.</v>
       </c>
       <c r="B51" s="3">
-        <v>46080</v>
+        <v>46062</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D51" s="4">
-        <v>0.375</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="E51" s="4">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="F51" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="F51" s="12">
         <f>IF(E51&gt;D51,E51-D51,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D51-E51),""))</f>
-        <v>4.1666666666666685E-2</v>
+        <v>4.166666666666663E-2</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="str">
         <f>IF(ISNUMBER(B52),LEFT(TEXT(B52,"TTTT"),2)&amp;".","")</f>
-        <v>Fr.</v>
+        <v>Sa.</v>
       </c>
       <c r="B52" s="3">
-        <v>46080</v>
+        <v>46067</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D52" s="4">
-        <v>0.39583333333333331</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E52" s="4">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="F52" s="5">
+        <v>0.875</v>
+      </c>
+      <c r="F52" s="12">
         <f>IF(E52&gt;D52,E52-D52,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D52-E52),""))</f>
-        <v>2.083333333333337E-2</v>
+        <v>0.20833333333333337</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="str">
         <f>IF(ISNUMBER(B53),LEFT(TEXT(B53,"TTTT"),2)&amp;".","")</f>
-        <v>Fr.</v>
+        <v>Sa.</v>
       </c>
       <c r="B53" s="3">
-        <v>46080</v>
+        <v>46067</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D53" s="4">
-        <v>0.63541666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="E53" s="4">
-        <v>0.69791666666666663</v>
-      </c>
-      <c r="F53" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="F53" s="12">
         <f>IF(E53&gt;D53,E53-D53,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D53-E53),""))</f>
-        <v>6.25E-2</v>
+        <v>0.16666666666666663</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="str">
-        <f t="shared" ref="A54:A56" si="7">IF(ISNUMBER(B54),LEFT(TEXT(B54,"TTTT"),2)&amp;".","")</f>
-        <v>Fr.</v>
+        <f>IF(ISNUMBER(B54),LEFT(TEXT(B54,"TTTT"),2)&amp;".","")</f>
+        <v>Sa.</v>
       </c>
       <c r="B54" s="3">
-        <v>46080</v>
+        <v>46067</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D54" s="4">
-        <v>0.97916666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="E54" s="4">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="F54" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="F54" s="12">
         <f>IF(E54&gt;D54,E54-D54,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D54-E54),""))</f>
-        <v>6.25E-2</v>
+        <v>0.16666666666666663</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>Sa.</v>
+        <f>IF(ISNUMBER(B55),LEFT(TEXT(B55,"TTTT"),2)&amp;".","")</f>
+        <v>Fr.</v>
       </c>
       <c r="B55" s="3">
-        <v>46081</v>
+        <v>46073</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D55" s="4">
-        <v>0.41666666666666669</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="E55" s="4">
-        <v>0.6875</v>
-      </c>
-      <c r="F55" s="5">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F55" s="12">
         <f>IF(E55&gt;D55,E55-D55,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D55-E55),""))</f>
-        <v>0.27083333333333331</v>
+        <v>0.125</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>Mo.</v>
+        <f>IF(ISNUMBER(B56),LEFT(TEXT(B56,"TTTT"),2)&amp;".","")</f>
+        <v>Sa.</v>
       </c>
       <c r="B56" s="3">
-        <v>45957</v>
+        <v>46074</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D56" s="4">
-        <v>0.41666666666666669</v>
+        <v>0.75</v>
       </c>
       <c r="E56" s="4">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="F56" s="5">
+        <v>0</v>
+      </c>
+      <c r="F56" s="12">
         <f>IF(E56&gt;D56,E56-D56,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D56-E56),""))</f>
-        <v>0.12499999999999994</v>
+        <v>0.25</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="str">
-        <f t="shared" ref="A57:A58" si="8">IF(ISNUMBER(B57),LEFT(TEXT(B57,"TTTT"),2)&amp;".","")</f>
-        <v>Mi.</v>
+        <f>IF(ISNUMBER(B57),LEFT(TEXT(B57,"TTTT"),2)&amp;".","")</f>
+        <v>Di.</v>
       </c>
       <c r="B57" s="3">
-        <v>45959</v>
+        <v>46077</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D57" s="4">
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="E57" s="4">
-        <v>0.83333333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="F57" s="5">
         <f>IF(E57&gt;D57,E57-D57,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D57-E57),""))</f>
-        <v>0.16666666666666674</v>
+        <v>6.25E-2</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>Do.</v>
+        <f>IF(ISNUMBER(B58),LEFT(TEXT(B58,"TTTT"),2)&amp;".","")</f>
+        <v>Fr.</v>
       </c>
       <c r="B58" s="3">
-        <v>45960</v>
+        <v>46080</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D58" s="4">
-        <v>0.83333333333333337</v>
+        <v>0.375</v>
       </c>
       <c r="E58" s="4">
-        <v>0.91666666666666663</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="F58" s="5">
         <f>IF(E58&gt;D58,E58-D58,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D58-E58),""))</f>
-        <v>8.3333333333333259E-2</v>
+        <v>4.1666666666666685E-2</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="str">
-        <f t="shared" ref="A59:A72" si="9">IF(ISNUMBER(B59),LEFT(TEXT(B59,"TTTT"),2)&amp;".","")</f>
-        <v>Sa.</v>
+        <f>IF(ISNUMBER(B59),LEFT(TEXT(B59,"TTTT"),2)&amp;".","")</f>
+        <v>Fr.</v>
       </c>
       <c r="B59" s="3">
-        <v>45962</v>
+        <v>46080</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D59" s="4">
-        <v>0.79166666666666663</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="E59" s="4">
-        <v>0.875</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="F59" s="5">
         <f>IF(E59&gt;D59,E59-D59,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D59-E59),""))</f>
-        <v>8.333333333333337E-2</v>
+        <v>2.083333333333337E-2</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v>So.</v>
+        <f>IF(ISNUMBER(B60),LEFT(TEXT(B60,"TTTT"),2)&amp;".","")</f>
+        <v>Fr.</v>
       </c>
       <c r="B60" s="3">
-        <v>45963</v>
+        <v>46080</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D60" s="4">
-        <v>0.83333333333333337</v>
+        <v>0.63541666666666663</v>
       </c>
       <c r="E60" s="4">
-        <v>0.91666666666666663</v>
+        <v>0.69791666666666663</v>
       </c>
       <c r="F60" s="5">
         <f>IF(E60&gt;D60,E60-D60,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D60-E60),""))</f>
-        <v>8.3333333333333259E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v>Mi.</v>
+        <f>IF(ISNUMBER(B61),LEFT(TEXT(B61,"TTTT"),2)&amp;".","")</f>
+        <v>Fr.</v>
       </c>
       <c r="B61" s="3">
-        <v>45980</v>
+        <v>46080</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D61" s="4">
-        <v>0.70833333333333337</v>
+        <v>0.97916666666666663</v>
       </c>
       <c r="E61" s="4">
-        <v>0.79166666666666663</v>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="F61" s="5">
         <f>IF(E61&gt;D61,E61-D61,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D61-E61),""))</f>
-        <v>8.3333333333333259E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v>Do.</v>
+        <f>IF(ISNUMBER(B62),LEFT(TEXT(B62,"TTTT"),2)&amp;".","")</f>
+        <v>Sa.</v>
       </c>
       <c r="B62" s="3">
-        <v>45974</v>
+        <v>46081</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D62" s="4">
-        <v>0.625</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="E62" s="4">
-        <v>0.75</v>
+        <v>0.6875</v>
       </c>
       <c r="F62" s="5">
         <f>IF(E62&gt;D62,E62-D62,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D62-E62),""))</f>
-        <v>0.125</v>
+        <v>0.27083333333333331</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(ISNUMBER(B63),LEFT(TEXT(B63,"TTTT"),2)&amp;".","")</f>
         <v>So.</v>
       </c>
       <c r="B63" s="3">
         <v>46082</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D63" s="4">
         <v>0.45833333333333331</v>
@@ -4040,14 +4056,14 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(ISNUMBER(B64),LEFT(TEXT(B64,"TTTT"),2)&amp;".","")</f>
         <v>So.</v>
       </c>
       <c r="B64" s="3">
         <v>46082</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D64" s="4">
         <v>0.45833333333333331</v>
@@ -4065,14 +4081,14 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(ISNUMBER(B65),LEFT(TEXT(B65,"TTTT"),2)&amp;".","")</f>
         <v>So.</v>
       </c>
       <c r="B65" s="3">
         <v>46082</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D65" s="4">
         <v>0.45833333333333331</v>
@@ -4090,14 +4106,14 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(ISNUMBER(B66),LEFT(TEXT(B66,"TTTT"),2)&amp;".","")</f>
         <v>So.</v>
       </c>
       <c r="B66" s="3">
         <v>46082</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D66" s="4">
         <v>0.29166666666666669</v>
@@ -4115,14 +4131,14 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(ISNUMBER(B67),LEFT(TEXT(B67,"TTTT"),2)&amp;".","")</f>
         <v>Mo.</v>
       </c>
       <c r="B67" s="3">
         <v>46083</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D67" s="4">
         <v>0.33333333333333331</v>
@@ -4140,64 +4156,64 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v>Di.</v>
+        <f>IF(ISNUMBER(B68),LEFT(TEXT(B68,"TTTT"),2)&amp;".","")</f>
+        <v>Mo.</v>
       </c>
       <c r="B68" s="3">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D68" s="4">
-        <v>0.49305555555555558</v>
+        <v>0.625</v>
       </c>
       <c r="E68" s="4">
-        <v>0.53472222222222221</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F68" s="5">
         <f>IF(E68&gt;D68,E68-D68,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D68-E68),""))</f>
-        <v>4.166666666666663E-2</v>
+        <v>8.333333333333337E-2</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v>Mo.</v>
+        <f>IF(ISNUMBER(B69),LEFT(TEXT(B69,"TTTT"),2)&amp;".","")</f>
+        <v>Di.</v>
       </c>
       <c r="B69" s="3">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D69" s="4">
-        <v>0.625</v>
+        <v>0.49305555555555558</v>
       </c>
       <c r="E69" s="4">
-        <v>0.70833333333333337</v>
+        <v>0.53472222222222221</v>
       </c>
       <c r="F69" s="5">
         <f>IF(E69&gt;D69,E69-D69,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D69-E69),""))</f>
-        <v>8.333333333333337E-2</v>
+        <v>4.166666666666663E-2</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(ISNUMBER(B70),LEFT(TEXT(B70,"TTTT"),2)&amp;".","")</f>
         <v>Di.</v>
       </c>
       <c r="B70" s="3">
         <v>46084</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D70" s="4">
         <v>0.625</v>
@@ -4215,14 +4231,14 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(ISNUMBER(B71),LEFT(TEXT(B71,"TTTT"),2)&amp;".","")</f>
         <v>Mi.</v>
       </c>
       <c r="B71" s="3">
         <v>46085</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D71" s="4">
         <v>0.625</v>
@@ -4240,14 +4256,14 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(ISNUMBER(B72),LEFT(TEXT(B72,"TTTT"),2)&amp;".","")</f>
         <v>Mi.</v>
       </c>
       <c r="B72" s="3">
         <v>46085</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D72" s="4">
         <v>0.4861111111111111</v>
@@ -4272,7 +4288,7 @@
         <v>46085</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D73" s="4">
         <v>0.83333333333333337</v>
@@ -4290,14 +4306,14 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="str">
-        <f t="shared" ref="A74:A77" si="10">IF(ISNUMBER(B74),LEFT(TEXT(B74,"TTTT"),2)&amp;".","")</f>
+        <f>IF(ISNUMBER(B74),LEFT(TEXT(B74,"TTTT"),2)&amp;".","")</f>
         <v>Do.</v>
       </c>
       <c r="B74" s="3">
         <v>46086</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D74" s="4">
         <v>0.45833333333333331</v>
@@ -4315,14 +4331,14 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(ISNUMBER(B75),LEFT(TEXT(B75,"TTTT"),2)&amp;".","")</f>
         <v>Do.</v>
       </c>
       <c r="B75" s="3">
         <v>46086</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D75" s="4">
         <v>0.75</v>
@@ -4340,33 +4356,128 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="B76" s="3"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="5" t="str">
+        <f>IF(ISNUMBER(B76),LEFT(TEXT(B76,"TTTT"),2)&amp;".","")</f>
+        <v>Fr.</v>
+      </c>
+      <c r="B76" s="3">
+        <v>46087</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D76" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E76" s="4">
+        <v>0.875</v>
+      </c>
+      <c r="F76" s="5">
         <f>IF(E76&gt;D76,E76-D76,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D76-E76),""))</f>
-        <v/>
-      </c>
-      <c r="G76" s="2"/>
+        <v>0.125</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="B77" s="3"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="5" t="str">
+        <f>IF(ISNUMBER(B77),LEFT(TEXT(B77,"TTTT"),2)&amp;".","")</f>
+        <v>Sa.</v>
+      </c>
+      <c r="B77" s="3">
+        <v>46088</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D77" s="4">
+        <v>0.625</v>
+      </c>
+      <c r="E77" s="4">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F77" s="5">
         <f>IF(E77&gt;D77,E77-D77,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D77-E77),""))</f>
-        <v/>
-      </c>
-      <c r="G77" s="2"/>
+        <v>8.333333333333337E-2</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="23" t="str">
+        <f>IF(ISNUMBER(B78),LEFT(TEXT(B78,"TTTT"),2)&amp;".","")</f>
+        <v>So.</v>
+      </c>
+      <c r="B78" s="3">
+        <v>46089</v>
+      </c>
+      <c r="C78" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="D78" s="4">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="E78" s="4">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F78" s="5">
+        <f>IF(E78&gt;D78,E78-D78,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D78-E78),""))</f>
+        <v>0.125</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="23" t="str">
+        <f>IF(ISNUMBER(B79),LEFT(TEXT(B79,"TTTT"),2)&amp;".","")</f>
+        <v>Mo.</v>
+      </c>
+      <c r="B79" s="3">
+        <v>46090</v>
+      </c>
+      <c r="C79" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D79" s="4">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E79" s="4">
+        <v>0.375</v>
+      </c>
+      <c r="F79" s="5">
+        <f>IF(E79&gt;D79,E79-D79,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D79-E79),""))</f>
+        <v>4.1666666666666685E-2</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="23" t="str">
+        <f>IF(ISNUMBER(B80),LEFT(TEXT(B80,"TTTT"),2)&amp;".","")</f>
+        <v>Mo.</v>
+      </c>
+      <c r="B80" s="3">
+        <v>46090</v>
+      </c>
+      <c r="C80" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="D80" s="4">
+        <v>0.375</v>
+      </c>
+      <c r="E80" s="4">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="F80" s="5">
+        <f>IF(E80&gt;D80,E80-D80,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D80-E80),""))</f>
+        <v>1.3888888888888895E-2</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/Stundenliste_neu(1).xlsx
+++ b/Stundenliste_neu(1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arthur.peer\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arthur\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B460BA97-566C-4DDD-B070-70B78D07C376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC00E6F-688B-4A48-8236-FE98741625B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{904973F5-B02B-4666-A03D-BB66738E721E}"/>
+    <workbookView xWindow="4650" yWindow="4350" windowWidth="28800" windowHeight="15435" xr2:uid="{904973F5-B02B-4666-A03D-BB66738E721E}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="92">
   <si>
     <t>Tag</t>
   </si>
@@ -309,6 +309,9 @@
   </si>
   <si>
     <t>Zeitmanagement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kleinere Fehler behoben; Diplo Leveldesign </t>
   </si>
 </sst>
 </file>
@@ -445,8 +448,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Prozent" xfId="1" builtinId="5"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -663,7 +666,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="de-DE"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -925,7 +928,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.70175438596490847</c:v>
+                  <c:v>0.71820175438596112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1933,8 +1936,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD71F5EC-BCBD-4D95-9F21-060EF7779827}" name="Stundenliste" displayName="Stundenliste" ref="A1:G80" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A1:G80" xr:uid="{730AE997-56E9-481C-8C9C-45C7D9E3EFFC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD71F5EC-BCBD-4D95-9F21-060EF7779827}" name="Stundenliste" displayName="Stundenliste" ref="A1:G81" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A1:G81" xr:uid="{730AE997-56E9-481C-8C9C-45C7D9E3EFFC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G80">
     <sortCondition ref="B1:B80"/>
   </sortState>
@@ -1992,9 +1995,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 – 2022">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2032,7 +2035,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 – 2022">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2138,7 +2141,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 – 2022">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2289,8 +2292,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{730198CE-52B5-4F02-9B4B-1774B163D30B}">
   <sheetPr codeName="Tabelle1"/>
-  <dimension ref="A1:Q80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q81"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.42578125" customWidth="1"/>
@@ -2326,7 +2329,7 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="str">
-        <f>IF(ISNUMBER(B2),LEFT(TEXT(B2,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" ref="A2:A33" si="0">IF(ISNUMBER(B2),LEFT(TEXT(B2,"TTTT"),2)&amp;".","")</f>
         <v>So.</v>
       </c>
       <c r="B2" s="3">
@@ -2375,7 +2378,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="str">
-        <f>IF(ISNUMBER(B3),LEFT(TEXT(B3,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Di.</v>
       </c>
       <c r="B3" s="3">
@@ -2421,7 +2424,7 @@
         <v>0.10555555555555557</v>
       </c>
       <c r="P3" s="22">
-        <f t="shared" ref="P3:P6" si="0">(O3/180)*100</f>
+        <f t="shared" ref="P3:P6" si="1">(O3/180)*100</f>
         <v>5.8641975308641986E-2</v>
       </c>
       <c r="Q3" s="21">
@@ -2431,7 +2434,7 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="str">
-        <f>IF(ISNUMBER(B4),LEFT(TEXT(B4,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Di.</v>
       </c>
       <c r="B4" s="3">
@@ -2465,28 +2468,28 @@
       </c>
       <c r="M4" s="11">
         <f>SUM(J5,J8,J9,J11)</f>
-        <v>5.333333333333333</v>
+        <v>5.458333333333333</v>
       </c>
       <c r="N4" s="18">
-        <f t="shared" ref="N4:N5" si="1">M4</f>
-        <v>5.333333333333333</v>
+        <f t="shared" ref="N4:N5" si="2">M4</f>
+        <v>5.458333333333333</v>
       </c>
       <c r="O4" s="18">
-        <f t="shared" ref="O4:O5" si="2">N4/60</f>
-        <v>8.8888888888888878E-2</v>
+        <f t="shared" ref="O4:O5" si="3">N4/60</f>
+        <v>9.0972222222222218E-2</v>
       </c>
       <c r="P4" s="22">
-        <f t="shared" si="0"/>
-        <v>4.9382716049382706E-2</v>
+        <f t="shared" si="1"/>
+        <v>5.0540123456790119E-2</v>
       </c>
       <c r="Q4" s="21">
-        <f t="shared" ref="Q4:Q5" si="3">(P4*1421.05263157894)/100</f>
-        <v>0.70175438596490847</v>
+        <f t="shared" ref="Q4:Q5" si="4">(P4*1421.05263157894)/100</f>
+        <v>0.71820175438596112</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="str">
-        <f>IF(ISNUMBER(B5),LEFT(TEXT(B5,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Di.</v>
       </c>
       <c r="B5" s="3">
@@ -2513,7 +2516,7 @@
       </c>
       <c r="J5" s="10">
         <f>SUMIF(Stundenliste[Wer],I5,Stundenliste[Stunden])</f>
-        <v>1.6458333333333335</v>
+        <v>1.7708333333333335</v>
       </c>
       <c r="L5" t="s">
         <v>9</v>
@@ -2523,25 +2526,25 @@
         <v>5.1874999999999991</v>
       </c>
       <c r="N5" s="18">
+        <f t="shared" si="2"/>
+        <v>5.1874999999999991</v>
+      </c>
+      <c r="O5" s="18">
+        <f t="shared" si="3"/>
+        <v>8.6458333333333318E-2</v>
+      </c>
+      <c r="P5" s="22">
         <f t="shared" si="1"/>
-        <v>5.1874999999999991</v>
-      </c>
-      <c r="O5" s="18">
-        <f t="shared" si="2"/>
-        <v>8.6458333333333318E-2</v>
-      </c>
-      <c r="P5" s="22">
-        <f t="shared" si="0"/>
         <v>4.8032407407407399E-2</v>
       </c>
       <c r="Q5" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.68256578947368052</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="str">
-        <f>IF(ISNUMBER(B6),LEFT(TEXT(B6,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Di.</v>
       </c>
       <c r="B6" s="3">
@@ -2574,7 +2577,7 @@
         <v>180</v>
       </c>
       <c r="P6" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="Q6" s="21">
@@ -2584,7 +2587,7 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="str">
-        <f>IF(ISNUMBER(B7),LEFT(TEXT(B7,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Di.</v>
       </c>
       <c r="B7" s="3">
@@ -2614,8 +2617,8 @@
         <v>0.77083333333333326</v>
       </c>
       <c r="M7" s="15">
-        <f>SUM(F2:F80)</f>
-        <v>9.5000000000000053</v>
+        <f>SUM(F2:F81)</f>
+        <v>9.6250000000000053</v>
       </c>
       <c r="N7">
         <v>180</v>
@@ -2623,7 +2626,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="str">
-        <f>IF(ISNUMBER(B8),LEFT(TEXT(B8,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Sa.</v>
       </c>
       <c r="B8" s="3">
@@ -2654,12 +2657,12 @@
       </c>
       <c r="M8" s="16">
         <f>TEXT(M7,"[h]")+TEXT(M7,"mm")/60</f>
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="str">
-        <f>IF(ISNUMBER(B9),LEFT(TEXT(B9,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Fr.</v>
       </c>
       <c r="B9" s="3">
@@ -2691,7 +2694,7 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="str">
-        <f>IF(ISNUMBER(B10),LEFT(TEXT(B10,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Sa.</v>
       </c>
       <c r="B10" s="3">
@@ -2718,7 +2721,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="str">
-        <f>IF(ISNUMBER(B11),LEFT(TEXT(B11,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Mi.</v>
       </c>
       <c r="B11" s="3">
@@ -2750,7 +2753,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="str">
-        <f>IF(ISNUMBER(B12),LEFT(TEXT(B12,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>So.</v>
       </c>
       <c r="B12" s="3">
@@ -2775,7 +2778,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="str">
-        <f>IF(ISNUMBER(B13),LEFT(TEXT(B13,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Fr.</v>
       </c>
       <c r="B13" s="3">
@@ -2803,7 +2806,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="str">
-        <f>IF(ISNUMBER(B14),LEFT(TEXT(B14,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Mo.</v>
       </c>
       <c r="B14" s="3">
@@ -2831,7 +2834,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="str">
-        <f>IF(ISNUMBER(B15),LEFT(TEXT(B15,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Mi.</v>
       </c>
       <c r="B15" s="3">
@@ -2856,7 +2859,7 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="str">
-        <f>IF(ISNUMBER(B16),LEFT(TEXT(B16,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Do.</v>
       </c>
       <c r="B16" s="3">
@@ -2881,7 +2884,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="str">
-        <f>IF(ISNUMBER(B17),LEFT(TEXT(B17,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Sa.</v>
       </c>
       <c r="B17" s="3">
@@ -2906,7 +2909,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="str">
-        <f>IF(ISNUMBER(B18),LEFT(TEXT(B18,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>So.</v>
       </c>
       <c r="B18" s="3">
@@ -2931,7 +2934,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="str">
-        <f>IF(ISNUMBER(B19),LEFT(TEXT(B19,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Fr.</v>
       </c>
       <c r="B19" s="3">
@@ -2956,7 +2959,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="str">
-        <f>IF(ISNUMBER(B20),LEFT(TEXT(B20,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Sa.</v>
       </c>
       <c r="B20" s="3">
@@ -2981,7 +2984,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="str">
-        <f>IF(ISNUMBER(B21),LEFT(TEXT(B21,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Sa.</v>
       </c>
       <c r="B21" s="3">
@@ -3006,7 +3009,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="str">
-        <f>IF(ISNUMBER(B22),LEFT(TEXT(B22,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Mi.</v>
       </c>
       <c r="B22" s="3">
@@ -3031,7 +3034,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="str">
-        <f>IF(ISNUMBER(B23),LEFT(TEXT(B23,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Do.</v>
       </c>
       <c r="B23" s="3">
@@ -3056,7 +3059,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="str">
-        <f>IF(ISNUMBER(B24),LEFT(TEXT(B24,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Mi.</v>
       </c>
       <c r="B24" s="3">
@@ -3081,7 +3084,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="str">
-        <f>IF(ISNUMBER(B25),LEFT(TEXT(B25,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Mi.</v>
       </c>
       <c r="B25" s="3">
@@ -3106,7 +3109,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="str">
-        <f>IF(ISNUMBER(B26),LEFT(TEXT(B26,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Do.</v>
       </c>
       <c r="B26" s="3">
@@ -3131,7 +3134,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="str">
-        <f>IF(ISNUMBER(B27),LEFT(TEXT(B27,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Fr.</v>
       </c>
       <c r="B27" s="3">
@@ -3156,7 +3159,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="str">
-        <f>IF(ISNUMBER(B28),LEFT(TEXT(B28,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Fr.</v>
       </c>
       <c r="B28" s="3">
@@ -3181,7 +3184,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="str">
-        <f>IF(ISNUMBER(B29),LEFT(TEXT(B29,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Sa.</v>
       </c>
       <c r="B29" s="3">
@@ -3206,7 +3209,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="str">
-        <f>IF(ISNUMBER(B30),LEFT(TEXT(B30,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Sa.</v>
       </c>
       <c r="B30" s="3">
@@ -3231,7 +3234,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="str">
-        <f>IF(ISNUMBER(B31),LEFT(TEXT(B31,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Fr.</v>
       </c>
       <c r="B31" s="3">
@@ -3256,7 +3259,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="str">
-        <f>IF(ISNUMBER(B32),LEFT(TEXT(B32,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Mo.</v>
       </c>
       <c r="B32" s="3">
@@ -3281,7 +3284,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="str">
-        <f>IF(ISNUMBER(B33),LEFT(TEXT(B33,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="0"/>
         <v>Mi.</v>
       </c>
       <c r="B33" s="3">
@@ -3306,7 +3309,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="str">
-        <f>IF(ISNUMBER(B34),LEFT(TEXT(B34,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" ref="A34:A65" si="5">IF(ISNUMBER(B34),LEFT(TEXT(B34,"TTTT"),2)&amp;".","")</f>
         <v>Mi.</v>
       </c>
       <c r="B34" s="3">
@@ -3331,7 +3334,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="str">
-        <f>IF(ISNUMBER(B35),LEFT(TEXT(B35,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>Mi.</v>
       </c>
       <c r="B35" s="3">
@@ -3356,7 +3359,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="str">
-        <f>IF(ISNUMBER(B36),LEFT(TEXT(B36,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>Mo.</v>
       </c>
       <c r="B36" s="3">
@@ -3381,7 +3384,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="str">
-        <f>IF(ISNUMBER(B37),LEFT(TEXT(B37,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>Mo.</v>
       </c>
       <c r="B37" s="3">
@@ -3406,7 +3409,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="str">
-        <f>IF(ISNUMBER(B38),LEFT(TEXT(B38,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>Fr.</v>
       </c>
       <c r="B38" s="3">
@@ -3431,7 +3434,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="str">
-        <f>IF(ISNUMBER(B39),LEFT(TEXT(B39,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>Fr.</v>
       </c>
       <c r="B39" s="3">
@@ -3456,7 +3459,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="str">
-        <f>IF(ISNUMBER(B40),LEFT(TEXT(B40,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>Mo.</v>
       </c>
       <c r="B40" s="3">
@@ -3481,7 +3484,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="str">
-        <f>IF(ISNUMBER(B41),LEFT(TEXT(B41,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>Mo.</v>
       </c>
       <c r="B41" s="3">
@@ -3506,7 +3509,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="str">
-        <f>IF(ISNUMBER(B42),LEFT(TEXT(B42,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>Fr.</v>
       </c>
       <c r="B42" s="3">
@@ -3531,7 +3534,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="str">
-        <f>IF(ISNUMBER(B43),LEFT(TEXT(B43,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>Sa.</v>
       </c>
       <c r="B43" s="3">
@@ -3556,7 +3559,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="str">
-        <f>IF(ISNUMBER(B44),LEFT(TEXT(B44,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>So.</v>
       </c>
       <c r="B44" s="3">
@@ -3581,7 +3584,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="str">
-        <f>IF(ISNUMBER(B45),LEFT(TEXT(B45,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>Fr.</v>
       </c>
       <c r="B45" s="3">
@@ -3606,7 +3609,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="str">
-        <f>IF(ISNUMBER(B46),LEFT(TEXT(B46,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>Fr.</v>
       </c>
       <c r="B46" s="3">
@@ -3631,7 +3634,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="str">
-        <f>IF(ISNUMBER(B47),LEFT(TEXT(B47,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>Sa.</v>
       </c>
       <c r="B47" s="3">
@@ -3656,7 +3659,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="str">
-        <f>IF(ISNUMBER(B48),LEFT(TEXT(B48,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>Di.</v>
       </c>
       <c r="B48" s="3">
@@ -3681,7 +3684,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="str">
-        <f>IF(ISNUMBER(B49),LEFT(TEXT(B49,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>Mi.</v>
       </c>
       <c r="B49" s="3">
@@ -3706,7 +3709,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="str">
-        <f>IF(ISNUMBER(B50),LEFT(TEXT(B50,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>Mi.</v>
       </c>
       <c r="B50" s="3">
@@ -3731,7 +3734,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="str">
-        <f>IF(ISNUMBER(B51),LEFT(TEXT(B51,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>Mo.</v>
       </c>
       <c r="B51" s="3">
@@ -3756,7 +3759,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="str">
-        <f>IF(ISNUMBER(B52),LEFT(TEXT(B52,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>Sa.</v>
       </c>
       <c r="B52" s="3">
@@ -3781,7 +3784,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="str">
-        <f>IF(ISNUMBER(B53),LEFT(TEXT(B53,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>Sa.</v>
       </c>
       <c r="B53" s="3">
@@ -3806,7 +3809,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="str">
-        <f>IF(ISNUMBER(B54),LEFT(TEXT(B54,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>Sa.</v>
       </c>
       <c r="B54" s="3">
@@ -3831,7 +3834,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="str">
-        <f>IF(ISNUMBER(B55),LEFT(TEXT(B55,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>Fr.</v>
       </c>
       <c r="B55" s="3">
@@ -3856,7 +3859,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="str">
-        <f>IF(ISNUMBER(B56),LEFT(TEXT(B56,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>Sa.</v>
       </c>
       <c r="B56" s="3">
@@ -3881,7 +3884,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="str">
-        <f>IF(ISNUMBER(B57),LEFT(TEXT(B57,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>Di.</v>
       </c>
       <c r="B57" s="3">
@@ -3906,7 +3909,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="str">
-        <f>IF(ISNUMBER(B58),LEFT(TEXT(B58,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>Fr.</v>
       </c>
       <c r="B58" s="3">
@@ -3931,7 +3934,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="str">
-        <f>IF(ISNUMBER(B59),LEFT(TEXT(B59,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>Fr.</v>
       </c>
       <c r="B59" s="3">
@@ -3956,7 +3959,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="str">
-        <f>IF(ISNUMBER(B60),LEFT(TEXT(B60,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>Fr.</v>
       </c>
       <c r="B60" s="3">
@@ -3981,7 +3984,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="str">
-        <f>IF(ISNUMBER(B61),LEFT(TEXT(B61,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>Fr.</v>
       </c>
       <c r="B61" s="3">
@@ -4006,7 +4009,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="str">
-        <f>IF(ISNUMBER(B62),LEFT(TEXT(B62,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>Sa.</v>
       </c>
       <c r="B62" s="3">
@@ -4031,7 +4034,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="str">
-        <f>IF(ISNUMBER(B63),LEFT(TEXT(B63,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>So.</v>
       </c>
       <c r="B63" s="3">
@@ -4056,7 +4059,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="str">
-        <f>IF(ISNUMBER(B64),LEFT(TEXT(B64,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>So.</v>
       </c>
       <c r="B64" s="3">
@@ -4081,7 +4084,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="str">
-        <f>IF(ISNUMBER(B65),LEFT(TEXT(B65,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="5"/>
         <v>So.</v>
       </c>
       <c r="B65" s="3">
@@ -4106,7 +4109,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="str">
-        <f>IF(ISNUMBER(B66),LEFT(TEXT(B66,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" ref="A66:A97" si="6">IF(ISNUMBER(B66),LEFT(TEXT(B66,"TTTT"),2)&amp;".","")</f>
         <v>So.</v>
       </c>
       <c r="B66" s="3">
@@ -4131,7 +4134,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="str">
-        <f>IF(ISNUMBER(B67),LEFT(TEXT(B67,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="6"/>
         <v>Mo.</v>
       </c>
       <c r="B67" s="3">
@@ -4156,7 +4159,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="str">
-        <f>IF(ISNUMBER(B68),LEFT(TEXT(B68,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="6"/>
         <v>Mo.</v>
       </c>
       <c r="B68" s="3">
@@ -4181,7 +4184,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="str">
-        <f>IF(ISNUMBER(B69),LEFT(TEXT(B69,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="6"/>
         <v>Di.</v>
       </c>
       <c r="B69" s="3">
@@ -4206,7 +4209,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="str">
-        <f>IF(ISNUMBER(B70),LEFT(TEXT(B70,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="6"/>
         <v>Di.</v>
       </c>
       <c r="B70" s="3">
@@ -4231,7 +4234,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="str">
-        <f>IF(ISNUMBER(B71),LEFT(TEXT(B71,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="6"/>
         <v>Mi.</v>
       </c>
       <c r="B71" s="3">
@@ -4256,7 +4259,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="str">
-        <f>IF(ISNUMBER(B72),LEFT(TEXT(B72,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="6"/>
         <v>Mi.</v>
       </c>
       <c r="B72" s="3">
@@ -4281,7 +4284,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="str">
-        <f>IF(ISNUMBER(B73),LEFT(TEXT(B73,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="6"/>
         <v>Mi.</v>
       </c>
       <c r="B73" s="3">
@@ -4306,7 +4309,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="str">
-        <f>IF(ISNUMBER(B74),LEFT(TEXT(B74,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="6"/>
         <v>Do.</v>
       </c>
       <c r="B74" s="3">
@@ -4331,7 +4334,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="str">
-        <f>IF(ISNUMBER(B75),LEFT(TEXT(B75,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="6"/>
         <v>Do.</v>
       </c>
       <c r="B75" s="3">
@@ -4356,7 +4359,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="str">
-        <f>IF(ISNUMBER(B76),LEFT(TEXT(B76,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="6"/>
         <v>Fr.</v>
       </c>
       <c r="B76" s="3">
@@ -4381,7 +4384,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="str">
-        <f>IF(ISNUMBER(B77),LEFT(TEXT(B77,"TTTT"),2)&amp;".","")</f>
+        <f t="shared" si="6"/>
         <v>Sa.</v>
       </c>
       <c r="B77" s="3">
@@ -4405,14 +4408,14 @@
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="23" t="str">
-        <f>IF(ISNUMBER(B78),LEFT(TEXT(B78,"TTTT"),2)&amp;".","")</f>
+      <c r="A78" s="2" t="str">
+        <f t="shared" si="6"/>
         <v>So.</v>
       </c>
       <c r="B78" s="3">
         <v>46089</v>
       </c>
-      <c r="C78" s="23" t="s">
+      <c r="C78" s="2" t="s">
         <v>87</v>
       </c>
       <c r="D78" s="4">
@@ -4430,14 +4433,14 @@
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="23" t="str">
-        <f>IF(ISNUMBER(B79),LEFT(TEXT(B79,"TTTT"),2)&amp;".","")</f>
+      <c r="A79" s="2" t="str">
+        <f t="shared" si="6"/>
         <v>Mo.</v>
       </c>
       <c r="B79" s="3">
         <v>46090</v>
       </c>
-      <c r="C79" s="23" t="s">
+      <c r="C79" s="2" t="s">
         <v>89</v>
       </c>
       <c r="D79" s="4">
@@ -4455,14 +4458,14 @@
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="23" t="str">
-        <f>IF(ISNUMBER(B80),LEFT(TEXT(B80,"TTTT"),2)&amp;".","")</f>
+      <c r="A80" s="2" t="str">
+        <f t="shared" si="6"/>
         <v>Mo.</v>
       </c>
       <c r="B80" s="3">
         <v>46090</v>
       </c>
-      <c r="C80" s="23" t="s">
+      <c r="C80" s="2" t="s">
         <v>90</v>
       </c>
       <c r="D80" s="4">
@@ -4476,6 +4479,31 @@
         <v>1.3888888888888895E-2</v>
       </c>
       <c r="G80" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="23" t="str">
+        <f>IF(ISNUMBER(B81),LEFT(TEXT(B81,"TTTT"),2)&amp;".","")</f>
+        <v>Mo.</v>
+      </c>
+      <c r="B81" s="3">
+        <v>46090</v>
+      </c>
+      <c r="C81" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="D81" s="4">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="E81" s="4">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="F81" s="5">
+        <f>IF(E81&gt;D81,E81-D81,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D81-E81),""))</f>
+        <v>0.125</v>
+      </c>
+      <c r="G81" s="2" t="s">
         <v>11</v>
       </c>
     </row>
@@ -4492,20 +4520,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <ReferenceId xmlns="d9f85066-e658-4e34-914c-f198c2427564" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <ReferenceId xmlns="d9f85066-e658-4e34-914c-f198c2427564" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4653,6 +4681,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A879EED-63D4-4BD6-ABDC-8DEB19CAAEDF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57E083A2-B59E-4178-BBDB-6F72551558F7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -4666,14 +4702,6 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="becce21f-4543-4ee3-84d8-746b4cf7c34b"/>
     <ds:schemaRef ds:uri="d9f85066-e658-4e34-914c-f198c2427564"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A879EED-63D4-4BD6-ABDC-8DEB19CAAEDF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
